--- a/www/download/IND.gdp.s.mv.EXI382.xlsx
+++ b/www/download/IND.gdp.s.mv.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>10093.519</t>
+          <t>10093519079.6486</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7975.528</t>
+          <t>7975527515.18724</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8046.917</t>
+          <t>8046916849.35512</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8126.6</t>
+          <t>8126599806.52603</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8226.269</t>
+          <t>8226269430.88191</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8225.809</t>
+          <t>8225808975.36749</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8478.735</t>
+          <t>8478734792.89538</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>8500.565</t>
+          <t>8500564820.00583</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>8557.01</t>
+          <t>8557010266.91289</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>8664.831</t>
+          <t>8664830531.76501</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>8897.021</t>
+          <t>8897020980.93651</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>9097.599</t>
+          <t>9097598814.29246</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>9377.484</t>
+          <t>9377483869.55889</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>9643.757</t>
+          <t>9643756759.43332</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>9956.806</t>
+          <t>9956806274.45176</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10109.002</t>
+          <t>10109002314.8111</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>10410.634</t>
+          <t>10410634025.3356</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>10508.974</t>
+          <t>10508973871.5855</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>10701.015</t>
+          <t>10701015043.8729</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>9615.754</t>
+          <t>9615753697.70684</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>9025.034</t>
+          <t>9025033523.08088</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>8994.09</t>
+          <t>8994090033.27657</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>9302.209</t>
+          <t>9302209219.87773</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9776.311</t>
+          <t>9776310856.31991</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>9377.672</t>
+          <t>9377671526.62478</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>9078.818</t>
+          <t>9078818492.34775</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>9197.884</t>
+          <t>9197883611.33321</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4036.174</t>
+          <t>4036173981.55603</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3639.828</t>
+          <t>3639827999.99984</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3679.851</t>
+          <t>3679851000.00028</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3697.627</t>
+          <t>3697627000.00081</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>3670.988</t>
+          <t>3670988000.00199</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3692.301</t>
+          <t>3692301000.00027</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3690.581</t>
+          <t>3690580999.99962</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3655.122</t>
+          <t>3655121999.99902</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>3607.859</t>
+          <t>3607859000.00089</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3628.008</t>
+          <t>3628008000.0007</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>3651.012</t>
+          <t>3651011999.99985</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3649.189</t>
+          <t>3649189000.00001</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>3623.569</t>
+          <t>3623569000.00116</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>3663.498</t>
+          <t>3663498000.00009</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>3708.32</t>
+          <t>3708319999.99964</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>3561.037</t>
+          <t>3561036999.99919</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3563.95</t>
+          <t>3563950000.00091</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3644.257</t>
+          <t>3644256999.99886</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>3609.675</t>
+          <t>3609674999.99933</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3535.094</t>
+          <t>3535094242.46509</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3531000206.77844</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3575.279</t>
+          <t>3575278634.50578</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3786.031</t>
+          <t>3786030782.76294</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>3913.965</t>
+          <t>3913965095.75933</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>4046.419</t>
+          <t>4046419197.89377</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>4065.82</t>
+          <t>4065819610.41689</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>4088.069</t>
+          <t>4088069281.28458</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3182.331</t>
+          <t>3182331288.89105</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2796.3</t>
+          <t>2796300000.00113</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2861.4</t>
+          <t>2861399999.99992</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2875999999.9996</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2902.2</t>
+          <t>2902199999.99833</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3075.9</t>
+          <t>3075899999.99976</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3136.3</t>
+          <t>3136300000.00034</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3149.2</t>
+          <t>3149199999.99964</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>3090.7</t>
+          <t>3090700000.00054</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3067.7</t>
+          <t>3067699999.99883</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>3073.8</t>
+          <t>3073799999.99921</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3085.7</t>
+          <t>3085699999.99945</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>3147.9</t>
+          <t>3147900000.00125</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3194000000.00037</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>3224.8</t>
+          <t>3224800000.00043</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3153000000.00041</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3174.4</t>
+          <t>3174400000.00002</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3207.8</t>
+          <t>3207800000.0008</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>3242.6</t>
+          <t>3242600000.00012</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3220.974</t>
+          <t>3220973788.10631</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>3029.605</t>
+          <t>3029604908.15997</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>3109.655</t>
+          <t>3109655490.45522</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>3127.966</t>
+          <t>3127965732.40575</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>3134.483</t>
+          <t>3134483054.71129</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3157.098</t>
+          <t>3157098260.25207</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>3227.466</t>
+          <t>3227466428.54815</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>3221.828</t>
+          <t>3221827855.57013</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5190.891</t>
+          <t>5190890911.10576</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4796.866</t>
+          <t>4796866363.5493</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4629.225</t>
+          <t>4629224936.68041</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4373.279</t>
+          <t>4373279290.97785</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4037.313</t>
+          <t>4037313115.88595</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4050.993</t>
+          <t>4050992577.56676</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3581.565</t>
+          <t>3581564532.97444</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3834.818</t>
+          <t>3834817813.55162</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>3786.001</t>
+          <t>3786000919.52514</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3853.302</t>
+          <t>3853302123.87734</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>3937.913</t>
+          <t>3937912995.19983</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3956.653</t>
+          <t>3956653138.14049</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4114.76</t>
+          <t>4114760071.40903</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4259.555</t>
+          <t>4259555336.17221</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4381.552</t>
+          <t>4381551896.79849</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>4011.83</t>
+          <t>4011830101.04368</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>3726.79</t>
+          <t>3726790074.97272</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3519.367</t>
+          <t>3519367005.26062</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>3461.392</t>
+          <t>3461391959.10451</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3309.746</t>
+          <t>3309746177.54372</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>3458.861</t>
+          <t>3458861127.69767</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>3569.675</t>
+          <t>3569675206.00338</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>3677.616</t>
+          <t>3677616334.19911</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>4329.367</t>
+          <t>4329367005.80317</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>4293.879</t>
+          <t>4293879175.59098</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>4660.872</t>
+          <t>4660872068.01544</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4945.564</t>
+          <t>4945563886.4365</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>104512.648</t>
+          <t>104512647610.502</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>101105.453</t>
+          <t>101105453362.043</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>97146.239</t>
+          <t>97146238674.2003</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>99732.908</t>
+          <t>99732907694.0296</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>99326.982</t>
+          <t>99326982053.1635</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>101791.309</t>
+          <t>101791308525.081</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>101483.028</t>
+          <t>101483027831.241</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>103228.508</t>
+          <t>103228508156.128</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>103528.539</t>
+          <t>103528538688.481</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>103804.725</t>
+          <t>103804725046.932</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>109824.294</t>
+          <t>109824294246.386</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>113011.085</t>
+          <t>113011084836.38</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>111028.384</t>
+          <t>111028384116.379</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>112996.353</t>
+          <t>112996352774.723</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>112155.055</t>
+          <t>112155055498.774</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>113369.573</t>
+          <t>113369573451.888</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>111396.171</t>
+          <t>111396170728.448</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>111457.707</t>
+          <t>111457707158.398</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>113592.728</t>
+          <t>113592728165.568</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>110814.005</t>
+          <t>110814004784.09</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>105925.327</t>
+          <t>105925327205.241</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>90947.806</t>
+          <t>90947806134.2995</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>92919.92</t>
+          <t>92919919929.153</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>99810.844</t>
+          <t>99810844010.6193</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>89708.048</t>
+          <t>89708047643.1901</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>92291.933</t>
+          <t>92291933338.81</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>94057.016</t>
+          <t>94057015882.6105</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>12005.131</t>
+          <t>12005130916.9524</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>12112.574</t>
+          <t>12112573999.9966</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9917.428</t>
+          <t>9917427999.99831</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10617.274</t>
+          <t>10617274000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10655.502</t>
+          <t>10655502000.0043</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13090.821</t>
+          <t>13090821000.0027</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13312.625</t>
+          <t>13312624999.9969</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13253.974</t>
+          <t>13253973999.9993</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13421.49</t>
+          <t>13421489999.9963</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13486.878</t>
+          <t>13486877999.9942</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>13893.577</t>
+          <t>13893577000.0067</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>11539.956</t>
+          <t>11539956000</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>14192.322</t>
+          <t>14192321999.9988</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>14362.38</t>
+          <t>14362380000.002</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>14342.489</t>
+          <t>14342488999.9936</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>11939.463</t>
+          <t>11939462999.9966</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>14134.02</t>
+          <t>14134019999.9978</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>14391.858</t>
+          <t>14391858000.01</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>14691.888</t>
+          <t>14691888000.0019</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>13846.425</t>
+          <t>13846424660.023</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>12605.65</t>
+          <t>12605649766.6908</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>12270.629</t>
+          <t>12270628817.117</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>11675.601</t>
+          <t>11675601487.4633</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12074.949</t>
+          <t>12074949318.1201</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>11780.734</t>
+          <t>11780733978.557</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11939.263</t>
+          <t>11939263119.6167</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>11951.466</t>
+          <t>11951465640.7116</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2435051.483</t>
+          <t>2435051483171.03</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1168271.039</t>
+          <t>1168271039292.54</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1181825.534</t>
+          <t>1181825534412.65</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1183367.096</t>
+          <t>1183367095801.68</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1149800.897</t>
+          <t>1149800897169.51</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1153717.158</t>
+          <t>1153717157900.19</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1151393.026</t>
+          <t>1151393025820.42</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1146709.761</t>
+          <t>1146709760585.66</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1147749.257</t>
+          <t>1147749257375.06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1124697.519</t>
+          <t>1124697518562.64</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>1114564.113</t>
+          <t>1114564112503.65</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>1161982.432</t>
+          <t>1161982431886.04</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1170176</t>
+          <t>1170175999506.49</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>1114877.57</t>
+          <t>1114877569939.45</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1056730.682</t>
+          <t>1056730681606.87</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1016898.231</t>
+          <t>1016898230575.85</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1085672.312</t>
+          <t>1085672311979.47</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1126660.947</t>
+          <t>1126660946712.84</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1131284.764</t>
+          <t>1131284763762.14</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>1186777.637</t>
+          <t>1186777636716.01</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>1262532.772</t>
+          <t>1262532771675.18</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>1525017.985</t>
+          <t>1525017984704.02</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>1514452.773</t>
+          <t>1514452773384.58</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>1591473.452</t>
+          <t>1591473451873.82</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1692272.625</t>
+          <t>1692272624700.72</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>1860677.181</t>
+          <t>1860677180845.85</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1953206.35</t>
+          <t>1953206350014.78</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>400.74</t>
+          <t>400739701.893071</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>253.043</t>
+          <t>253042956.005576</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>253.397</t>
+          <t>253396944.058067</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>254.67</t>
+          <t>254669735.229846</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>254.593</t>
+          <t>254592584.429379</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>253.042</t>
+          <t>253042270.860227</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>259.232</t>
+          <t>259231507.735662</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>272.726</t>
+          <t>272726031.43565</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>274.524</t>
+          <t>274524162.260018</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>279.271</t>
+          <t>279271308.319858</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>302.575</t>
+          <t>302575301.222266</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>314.046</t>
+          <t>314046465.18358</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>313.242</t>
+          <t>313241777.019473</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>331.912</t>
+          <t>331911991.015491</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>346.139</t>
+          <t>346138527.258103</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>331.541</t>
+          <t>331540774.251416</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>334.986</t>
+          <t>334985627.302348</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>327.37</t>
+          <t>327369593.54605</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>310.349</t>
+          <t>310348660.067754</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>283.244</t>
+          <t>283243780.28115</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>252.847</t>
+          <t>252846611.998078</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>271.074</t>
+          <t>271074293.967461</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>304.276</t>
+          <t>304276143.248424</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>327.569</t>
+          <t>327569198.532852</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>348.776</t>
+          <t>348776352.647907</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>374.067</t>
+          <t>374067462.305593</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>370.172</t>
+          <t>370172400.065626</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>7289.017</t>
+          <t>7289017273.98609</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5891.029</t>
+          <t>5891029000.00063</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6040.175</t>
+          <t>6040175000.00126</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5948.673</t>
+          <t>5948673000.00042</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5903.583</t>
+          <t>5903582999.99761</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5752.434</t>
+          <t>5752433999.99965</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5663.356</t>
+          <t>5663355999.99889</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5223.868</t>
+          <t>5223867999.99868</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>5366.916</t>
+          <t>5366916000.00081</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>5270.736</t>
+          <t>5270736000.00022</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>5361.128</t>
+          <t>5361128000.00012</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>5445.23</t>
+          <t>5445229999.99931</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>5414.904</t>
+          <t>5414904000.00179</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>5459.189</t>
+          <t>5459189000.00028</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>5547.104</t>
+          <t>5547104000.00061</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>5315.102</t>
+          <t>5315102000.00157</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>5328.862</t>
+          <t>5328862000.00072</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>5186.535</t>
+          <t>5186534999.99931</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>5341.172</t>
+          <t>5341171999.99932</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>5033.453</t>
+          <t>5033452691.61868</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>4907.451</t>
+          <t>4907450647.9547</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5245.57</t>
+          <t>5245570070.41597</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>5326.309</t>
+          <t>5326308803.59312</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>5635.319</t>
+          <t>5635319026.20078</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>6074.357</t>
+          <t>6074356584.01485</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>6504.557</t>
+          <t>6504556789.34119</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>6617.812</t>
+          <t>6617811795.30257</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>33692.752</t>
+          <t>33692751670.5659</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32174.7</t>
+          <t>32174699999.9988</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>31871.9</t>
+          <t>31871900000.0083</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>31402.3</t>
+          <t>31402299999.996</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>31480.6</t>
+          <t>31480599999.9911</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>31596.4</t>
+          <t>31596400000.0056</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>31389</t>
+          <t>31388999999.9933</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>30862.3</t>
+          <t>30862299999.9975</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30426.5</t>
+          <t>30426500000.0052</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>29878.7</t>
+          <t>29878700000.0043</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>29852.2</t>
+          <t>29852199999.9967</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>29368.6</t>
+          <t>29368599999.9849</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>29721.5</t>
+          <t>29721499999.995</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>30137.5</t>
+          <t>30137500000.0039</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>30494.1</t>
+          <t>30494099999.999</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>29349.7</t>
+          <t>29349699999.9991</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>29951.5</t>
+          <t>29951499999.9922</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>30619.2</t>
+          <t>30619199999.9939</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>30722.2</t>
+          <t>30722199999.9895</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>31593.913</t>
+          <t>31593913257.3062</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>32106.48</t>
+          <t>32106479534.5123</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>30958.718</t>
+          <t>30958718055.2778</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>31369.939</t>
+          <t>31369938885.8476</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>33750.72</t>
+          <t>33750719737.0059</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>33053.177</t>
+          <t>33053177367.6225</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>33373.265</t>
+          <t>33373264925.0711</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>34191.442</t>
+          <t>34191442285.1365</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3035.867</t>
+          <t>3035866688.31997</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2972.025</t>
+          <t>2972024723.05939</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2964.639</t>
+          <t>2964639172.39501</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2672.707</t>
+          <t>2672707320.15265</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2211.83</t>
+          <t>2211830150.11329</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3126.239</t>
+          <t>3126239438.34664</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2991.446</t>
+          <t>2991446161.20905</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>3021.11</t>
+          <t>3021109707.08283</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>3056.856</t>
+          <t>3056856009.55513</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2955.608</t>
+          <t>2955608215.70939</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>3025.201</t>
+          <t>3025200945.96657</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3107.562</t>
+          <t>3107561656.04062</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>3107.902</t>
+          <t>3107901627.12091</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>3151.37</t>
+          <t>3151369934.96923</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>3055.475</t>
+          <t>3055475199.23828</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2805.739</t>
+          <t>2805738573.10699</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>2832.882</t>
+          <t>2832882034.70244</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>2881.234</t>
+          <t>2881233838.94597</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2866.861</t>
+          <t>2866861268.028</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>2770.091</t>
+          <t>2770091304.27553</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>2984.266</t>
+          <t>2984266334.55156</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>2798.071</t>
+          <t>2798071224.20178</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2805.955</t>
+          <t>2805954727.14869</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>2861.833</t>
+          <t>2861833343.19286</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2760.44</t>
+          <t>2760439976.94833</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2595.621</t>
+          <t>2595621139.21682</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2846.812</t>
+          <t>2846812008.41906</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16812.085</t>
+          <t>16812084709.312</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>14363.629</t>
+          <t>14363629326.5151</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14385.815</t>
+          <t>14385814683.438</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>15079.798</t>
+          <t>15079798169.4709</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>15776.566</t>
+          <t>15776566454.7497</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17038.431</t>
+          <t>17038431263.3298</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>17284.973</t>
+          <t>17284973285.3851</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18028.597</t>
+          <t>18028597432.5191</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>18678.273</t>
+          <t>18678272719.1849</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>18964.199</t>
+          <t>18964199220.2426</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>19694.904</t>
+          <t>19694903859.5655</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>21222.623</t>
+          <t>21222623176.5389</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>21725.799</t>
+          <t>21725798545.3908</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>22073.606</t>
+          <t>22073606202.916</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>20883.145</t>
+          <t>20883144862.9487</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>18549.346</t>
+          <t>18549345930.8088</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>17867.011</t>
+          <t>17867010896.9215</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>17229.16</t>
+          <t>17229159820.7789</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>16170.598</t>
+          <t>16170598494.1149</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>15471.557</t>
+          <t>15471557430.6123</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>15206.13</t>
+          <t>15206130496.7365</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>15964.251</t>
+          <t>15964250923.1019</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>16012.937</t>
+          <t>16012936520.8841</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16323.866</t>
+          <t>16323865885.7625</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>16909.222</t>
+          <t>16909221820.6071</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16725.223</t>
+          <t>16725222969.0567</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>16843.766</t>
+          <t>16843765971.4328</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1867.652</t>
+          <t>1867652053.47228</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>891.807</t>
+          <t>891807044.668045</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>852.795</t>
+          <t>852795331.719812</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>836.708</t>
+          <t>836707576.717821</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>826.677</t>
+          <t>826676571.848375</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>770.761</t>
+          <t>770760917.40764</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>787.577</t>
+          <t>787577161.701979</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>771.042</t>
+          <t>771041737.347937</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>731.012</t>
+          <t>731011608.120402</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>745.768</t>
+          <t>745767745.706854</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>764.022</t>
+          <t>764022007.871548</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>797.096</t>
+          <t>797096351.980397</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>849.298</t>
+          <t>849297884.639422</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>857.763</t>
+          <t>857763311.106996</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>841.65</t>
+          <t>841650300.056815</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>729.242</t>
+          <t>729241820.254717</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>693.875</t>
+          <t>693874620.705989</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>759.669</t>
+          <t>759668971.825539</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>769.586</t>
+          <t>769586291.952021</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>760.076</t>
+          <t>760075627.099415</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>754.467</t>
+          <t>754466571.88532</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>748.43</t>
+          <t>748429544.447415</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>777.143</t>
+          <t>777142678.73463</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>812.011</t>
+          <t>812010856.546908</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>861.731</t>
+          <t>861731214.122537</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>924.032</t>
+          <t>924032274.826461</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>951.296</t>
+          <t>951296176.907745</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2664.7</t>
+          <t>2664699981.77044</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2566.8</t>
+          <t>2566800108.80876</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2631.492</t>
+          <t>2631491925.97292</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2875.64</t>
+          <t>2875640497.805</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2876.984</t>
+          <t>2876984231.39058</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2927.637</t>
+          <t>2927636523.8235</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2939.877</t>
+          <t>2939877358.866</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2915.833</t>
+          <t>2915832562.68029</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2926.707</t>
+          <t>2926707404.72239</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2843.064</t>
+          <t>2843063698.20494</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2840.886</t>
+          <t>2840886238.58517</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2892.19</t>
+          <t>2892190151.34009</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2917.359</t>
+          <t>2917359419.68206</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2929.652</t>
+          <t>2929651961.61163</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2609.518</t>
+          <t>2609517940.70112</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2773.717</t>
+          <t>2773716586.50165</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>2762.69</t>
+          <t>2762690277.713</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>2780.817</t>
+          <t>2780817162.35018</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2758.647</t>
+          <t>2758647390.09279</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>2661.354</t>
+          <t>2661353968.42456</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>2728.507</t>
+          <t>2728507488.94878</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>2697.129</t>
+          <t>2697128591.05493</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2759.088</t>
+          <t>2759088200.59761</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>2800.758</t>
+          <t>2800757688.45321</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2968.126</t>
+          <t>2968126198.34387</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2825.767</t>
+          <t>2825766937.58723</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2850.768</t>
+          <t>2850767769.77969</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17361.874</t>
+          <t>17361873583.4988</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19871.3</t>
+          <t>19871299999.9942</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20078.5</t>
+          <t>20078500000.0016</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>20003.1</t>
+          <t>20003100000.0004</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>19969.6</t>
+          <t>19969600000.0005</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>20132.4</t>
+          <t>20132399999.9996</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>19939.4</t>
+          <t>19939399999.9957</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>19941.6</t>
+          <t>19941600000.0056</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>19442.9</t>
+          <t>19442900000.0032</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>19365.3</t>
+          <t>19365300000.0062</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>19735.1</t>
+          <t>19735100000.0111</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>19746.9</t>
+          <t>19746899999.9943</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>19667.8</t>
+          <t>19667800000.0006</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20110000000.0077</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>20286.4</t>
+          <t>20286400000.0075</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>19875.9</t>
+          <t>19875899999.997</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>19854.9</t>
+          <t>19854899999.9929</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>19955.4</t>
+          <t>19955400000.0039</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>19845.1</t>
+          <t>19845100000.0046</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>19000.929</t>
+          <t>19000928901.5394</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>18930.128</t>
+          <t>18930127530.7992</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>18700.397</t>
+          <t>18700396534.4827</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>18342.356</t>
+          <t>18342355725.2621</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18325.904</t>
+          <t>18325904239.7595</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>18228.445</t>
+          <t>18228445124.0985</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18266.988</t>
+          <t>18266987884.925</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>18282.903</t>
+          <t>18282902591.5622</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>34629.753</t>
+          <t>34629752803.5204</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27436.73</t>
+          <t>27436730292.7606</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28839.854</t>
+          <t>28839853733.907</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>28799.043</t>
+          <t>28799042923.1088</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>29110.004</t>
+          <t>29110004029.1382</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>28608.245</t>
+          <t>28608244755.5897</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>28667.991</t>
+          <t>28667990679.3029</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>28961.603</t>
+          <t>28961603306.9992</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>28932.797</t>
+          <t>28932796673.6997</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>28708.847</t>
+          <t>28708846833.5645</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>28859.908</t>
+          <t>28859907799.6023</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>29502.52</t>
+          <t>29502519774.6798</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>29854.286</t>
+          <t>29854285650.7932</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>29965.525</t>
+          <t>29965524883.2669</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>28986.863</t>
+          <t>28986863150.1188</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>27996.4</t>
+          <t>27996400169.4264</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>27975.437</t>
+          <t>27975436987.5695</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>28142.022</t>
+          <t>28142022182.2748</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>28358.91</t>
+          <t>28358909681.3981</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>28178.717</t>
+          <t>28178717358.6397</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>30712.97</t>
+          <t>30712970219.2171</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>35592.411</t>
+          <t>35592410799.2934</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>31397.297</t>
+          <t>31397297214.5051</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>30562.425</t>
+          <t>30562424871.9803</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>32078.988</t>
+          <t>32078987743.1626</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>33416.795</t>
+          <t>33416795118.0902</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>33791.383</t>
+          <t>33791383364.5422</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3722.374</t>
+          <t>3722373810.52577</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5012.323</t>
+          <t>5012323031.21134</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5028.485</t>
+          <t>5028485270.19358</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4904.785</t>
+          <t>4904784759.38926</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>5034.503</t>
+          <t>5034503147.21741</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5078.76</t>
+          <t>5078759908.59338</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>5064.175</t>
+          <t>5064174932.66788</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5043.168</t>
+          <t>5043168439.14074</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>5003.576</t>
+          <t>5003575942.35569</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>5139.329</t>
+          <t>5139329118.69752</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>5071.218</t>
+          <t>5071218419.64474</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>5018.062</t>
+          <t>5018062193.56142</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>5014.445</t>
+          <t>5014445197.08085</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>5012.801</t>
+          <t>5012801286.55911</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4860.18</t>
+          <t>4860179509.32998</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>4688.598</t>
+          <t>4688597968.93137</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>4580.254</t>
+          <t>4580254116.28406</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>4134.064</t>
+          <t>4134063879.13666</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>3810.007</t>
+          <t>3810007239.62241</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>3470.474</t>
+          <t>3470474039.03485</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>3085.436</t>
+          <t>3085435994.99858</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>3107.567</t>
+          <t>3107566563.58606</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2956.688</t>
+          <t>2956687838.71574</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3298.786</t>
+          <t>3298786273.30275</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>3355.365</t>
+          <t>3355365173.48269</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>3457.5</t>
+          <t>3457499639.10505</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>3541.071</t>
+          <t>3541071352.77777</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5593.914</t>
+          <t>5593913526.11359</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>5259.359</t>
+          <t>5259359071.51702</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>5170.235</t>
+          <t>5170234890.51896</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>5139.603</t>
+          <t>5139603104.56345</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>5225.56</t>
+          <t>5225560036.48117</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>5342.416</t>
+          <t>5342415790.91461</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5243.883</t>
+          <t>5243882971.07091</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5379.386</t>
+          <t>5379385956.78632</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>5173.378</t>
+          <t>5173377631.32784</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>5274.542</t>
+          <t>5274542278.40936</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5237.236</t>
+          <t>5237236030.27252</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4910.334</t>
+          <t>4910333507.90836</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>5111.978</t>
+          <t>5111978339.33083</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>5047.362</t>
+          <t>5047361749.27597</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>4686.383</t>
+          <t>4686383275.10243</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>4634.214</t>
+          <t>4634214233.28424</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>4618.92</t>
+          <t>4618919688.09307</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>4646.694</t>
+          <t>4646693802.32115</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4613.544</t>
+          <t>4613543728.49025</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>4604.461</t>
+          <t>4604461399.1358</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>4589.845</t>
+          <t>4589845329.2391</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>4867.196</t>
+          <t>4867195951.25445</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>4814.928</t>
+          <t>4814928077.02109</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5198.42</t>
+          <t>5198420282.15207</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>5641.122</t>
+          <t>5641121636.6202</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>5847.021</t>
+          <t>5847020847.00904</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>6003.076</t>
+          <t>6003076284.69825</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1807476.478</t>
+          <t>1807476477930.58</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>727141.552</t>
+          <t>727141551597.863</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>735735.944</t>
+          <t>735735944144.833</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>733792.045</t>
+          <t>733792044778.106</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>730779.172</t>
+          <t>730779171808.067</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>747111.599</t>
+          <t>747111599359.071</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>796948.864</t>
+          <t>796948863992.633</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>784589.923</t>
+          <t>784589922622.928</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>759077.977</t>
+          <t>759077977153.23</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>787734.495</t>
+          <t>787734495463.498</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>782955.523</t>
+          <t>782955522834.875</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>776722.859</t>
+          <t>776722858554.144</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>770319.877</t>
+          <t>770319877213.935</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>770896.23</t>
+          <t>770896230304.119</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>769635</t>
+          <t>769635000233.856</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>769330.437</t>
+          <t>769330436801.472</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>759562.646</t>
+          <t>759562646413.821</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>762709.861</t>
+          <t>762709861256.132</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>764970.576</t>
+          <t>764970575945.151</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>764590.71</t>
+          <t>764590710497.577</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>800610.226</t>
+          <t>800610226345.74</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>979045.952</t>
+          <t>979045951692.52</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1048414.966</t>
+          <t>1048414966302.94</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1172429.259</t>
+          <t>1172429258878.14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1159608.314</t>
+          <t>1159608313806.8</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>1287030.04</t>
+          <t>1287030040214.07</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>1375787.926</t>
+          <t>1375787925615.09</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>228038.333</t>
+          <t>228038333303.144</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>106272.027</t>
+          <t>106272026601.154</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>112832.836</t>
+          <t>112832836307.25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>112953.72</t>
+          <t>112953720078.596</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>113825.211</t>
+          <t>113825210959.758</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>115215.534</t>
+          <t>115215534043.087</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>115277.645</t>
+          <t>115277645284.576</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>118344.023</t>
+          <t>118344023129.663</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>115578.923</t>
+          <t>115578923322.908</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>119134.951</t>
+          <t>119134950928.608</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>126710.162</t>
+          <t>126710162395.147</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>128136.92</t>
+          <t>128136920328.945</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>127294.622</t>
+          <t>127294621570.01</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>130529.358</t>
+          <t>130529357636.026</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>138820.51</t>
+          <t>138820510293.872</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>134405.533</t>
+          <t>134405533004.719</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>138178.658</t>
+          <t>138178658241.367</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>128569.672</t>
+          <t>128569672190.384</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>140511.15</t>
+          <t>140511149742.265</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>139162.173</t>
+          <t>139162172815.572</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>130091.844</t>
+          <t>130091843740.597</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>160466.748</t>
+          <t>160466747527.588</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>171113.742</t>
+          <t>171113742096.898</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>180943.453</t>
+          <t>180943453061.026</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>174573.479</t>
+          <t>174573479232.426</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>195743.908</t>
+          <t>195743908479.826</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>206254.431</t>
+          <t>206254430976.033</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>4306.172</t>
+          <t>4306172180.8343</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>1552.723</t>
+          <t>1552722975.30023</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1616.764</t>
+          <t>1616764135.89572</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1717.642</t>
+          <t>1717642472.88845</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>1766.873</t>
+          <t>1766872926.54309</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1870.864</t>
+          <t>1870864051.41184</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1925.501</t>
+          <t>1925500769.12578</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1965.525</t>
+          <t>1965525389.9568</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>1918.428</t>
+          <t>1918427646.06387</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1990.523</t>
+          <t>1990523250.52005</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2039.476</t>
+          <t>2039475795.23571</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2152.136</t>
+          <t>2152136425.84888</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2245.603</t>
+          <t>2245602628.37888</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2290.911</t>
+          <t>2290910540.10904</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2205.047</t>
+          <t>2205047497.05344</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1926.611</t>
+          <t>1926611089.48485</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>1801.214</t>
+          <t>1801213996.43337</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>1760.799</t>
+          <t>1760798963.22697</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>1749.44</t>
+          <t>1749439699.42895</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>1864.951</t>
+          <t>1864950835.23946</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>1986.256</t>
+          <t>1986256072.55987</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>2842.975</t>
+          <t>2842974791.0868</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>3240.608</t>
+          <t>3240608432.27309</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>3296.316</t>
+          <t>3296315816.86825</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>3422.099</t>
+          <t>3422098530.84714</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>3879.469</t>
+          <t>3879468803.81271</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>4058.546</t>
+          <t>4058546141.50192</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20006.175</t>
+          <t>20006174730.9367</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>24591.997</t>
+          <t>24591996570.1042</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>23915.228</t>
+          <t>23915227778.0326</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>24333.661</t>
+          <t>24333660792.7811</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>24562.088</t>
+          <t>24562087954.6869</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>24372.91</t>
+          <t>24372909773.6332</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>24454.866</t>
+          <t>24454865735.1004</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25525.737</t>
+          <t>25525737461.9652</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>22892.9</t>
+          <t>22892900294.5082</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>25305.749</t>
+          <t>25305748869.5939</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>25255.429</t>
+          <t>25255429084.467</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>25051.925</t>
+          <t>25051924641.2016</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>25161.63</t>
+          <t>25161629657.4847</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>25272.043</t>
+          <t>25272042773.7043</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>24452.854</t>
+          <t>24452853751.8059</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>23676.192</t>
+          <t>23676191661.8669</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>23428.044</t>
+          <t>23428044005.372</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>23317.321</t>
+          <t>23317321195.1803</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>22623.829</t>
+          <t>22623828722.4789</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>21878.05</t>
+          <t>21878049874.9597</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>21324.749</t>
+          <t>21324748643.3357</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>21286.866</t>
+          <t>21286866355.7034</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>21181.24</t>
+          <t>21181240041.6626</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>21491.123</t>
+          <t>21491123463.6185</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>21857.307</t>
+          <t>21857306565.6703</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>21148.053</t>
+          <t>21148052615.865</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>21119.577</t>
+          <t>21119576543.0431</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>54426.037</t>
+          <t>54426036843.679</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>87325.176</t>
+          <t>87325175955.9603</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>87300.527</t>
+          <t>87300526973.1898</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>88017.112</t>
+          <t>88017111958.9565</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>86385.844</t>
+          <t>86385843828.8558</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>85277.197</t>
+          <t>85277197055.945</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>84806.447</t>
+          <t>84806446808.7704</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>83592.916</t>
+          <t>83592915886.3778</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>82127.316</t>
+          <t>82127316202.5599</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>76848.146</t>
+          <t>76848145796.3306</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>76153.928</t>
+          <t>76153928123.7062</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>76097.456</t>
+          <t>76097455963.7168</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>76376.636</t>
+          <t>76376635840.9382</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>76616.978</t>
+          <t>76616977645.1348</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>70505.288</t>
+          <t>70505287522.1743</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>72479.138</t>
+          <t>72479138447.2414</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>71863.459</t>
+          <t>71863458736.015</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>72243.309</t>
+          <t>72243308707.5425</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>72383.867</t>
+          <t>72383866550.6584</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>55642.776</t>
+          <t>55642775997.8649</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>57595.7</t>
+          <t>57595700102.7962</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>58199.958</t>
+          <t>58199958424.5124</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>60989.112</t>
+          <t>60989111552.5992</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>58505.292</t>
+          <t>58505291574.8122</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>55908.651</t>
+          <t>55908650971.6234</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>58912.569</t>
+          <t>58912569121.4844</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>58067.781</t>
+          <t>58067781182.5493</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>46704.994</t>
+          <t>46704994484.721</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>27513.917</t>
+          <t>27513916710.5055</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>27432.192</t>
+          <t>27432192315.9808</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>27271.47</t>
+          <t>27271470368.8287</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>25025.315</t>
+          <t>25025315286.4199</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>24877.721</t>
+          <t>24877721075.604</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>26475.314</t>
+          <t>26475314207.8841</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>26718.98</t>
+          <t>26718979954.1648</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>27544.571</t>
+          <t>27544570701.9999</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>27622.393</t>
+          <t>27622393476.479</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>28014.601</t>
+          <t>28014601382.4763</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>28182.226</t>
+          <t>28182225726.8857</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>28456.4</t>
+          <t>28456400329.4622</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>28432.318</t>
+          <t>28432317522.4021</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>29150.068</t>
+          <t>29150067695.4941</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>28627.209</t>
+          <t>28627208693.9023</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>29128.73</t>
+          <t>29128729850.3464</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>29539.268</t>
+          <t>29539267695.7497</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>29912.213</t>
+          <t>29912213002.5058</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>29491.684</t>
+          <t>29491684051.1605</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>32222.401</t>
+          <t>32222401240.6791</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>38909.961</t>
+          <t>38909961488.087</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>38851.937</t>
+          <t>38851937475.2029</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>41233.621</t>
+          <t>41233621221.4173</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>41002.192</t>
+          <t>41002191898.1997</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>41045.377</t>
+          <t>41045376949.7922</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>40763.345</t>
+          <t>40763345126.0177</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2313.165</t>
+          <t>2313165399.49036</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2495.521</t>
+          <t>2495520899.13575</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2512.344</t>
+          <t>2512343650.66576</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2448.176</t>
+          <t>2448175974.51419</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2431000256.78925</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2343.819</t>
+          <t>2343819212.83045</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2188.449</t>
+          <t>2188449393.69226</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2051.316</t>
+          <t>2051315946.00387</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2068.796</t>
+          <t>2068795590.07109</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2100.539</t>
+          <t>2100538818.74638</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1954.552</t>
+          <t>1954551535.91253</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>1994.703</t>
+          <t>1994703343.29273</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1956.391</t>
+          <t>1956390960.78991</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2001.325</t>
+          <t>2001325123.83475</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1853.31</t>
+          <t>1853309971.42144</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1642.067</t>
+          <t>1642067097.43882</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1541.651</t>
+          <t>1541650784.33976</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1545.542</t>
+          <t>1545542299.86241</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1578.759</t>
+          <t>1578759083.76194</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>1561.322</t>
+          <t>1561322303.64536</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>1634.559</t>
+          <t>1634559058.92381</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1651.288</t>
+          <t>1651288269.19836</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1673.43</t>
+          <t>1673430117.18802</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1828.313</t>
+          <t>1828313378.82478</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1956.285</t>
+          <t>1956284845.777</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026.337</t>
+          <t>2026337165.52351</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>2073.295</t>
+          <t>2073294551.15144</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>259.713</t>
+          <t>259712601.670991</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>164.909</t>
+          <t>164909043.258945</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>159.41</t>
+          <t>159410174.705552</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>161.03</t>
+          <t>161030245.338828</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>153.552</t>
+          <t>153551997.600638</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>161.546</t>
+          <t>161546486.253844</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>157.949</t>
+          <t>157948772.376516</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>163.533</t>
+          <t>163533256.452512</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>164.383</t>
+          <t>164383293.253354</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>163.2</t>
+          <t>163199539.449619</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>156.511</t>
+          <t>156510730.441613</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>159.413</t>
+          <t>159412537.388463</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>170.025</t>
+          <t>170025356.549252</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>169.091</t>
+          <t>169090871.454267</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>166.29</t>
+          <t>166289674.047494</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>160.725</t>
+          <t>160725289.298676</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>157.584</t>
+          <t>157584245.87148</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>163.039</t>
+          <t>163038969.813329</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>177.393</t>
+          <t>177393139.019845</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>181.06</t>
+          <t>181060235.665746</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>212.685</t>
+          <t>212685437.046823</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>227.105</t>
+          <t>227104966.753389</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>237.067</t>
+          <t>237067134.453503</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>227.77</t>
+          <t>227769797.619859</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>237.51</t>
+          <t>237510308.376104</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>247.555</t>
+          <t>247554901.472383</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>254.595</t>
+          <t>254594913.046604</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1680.062</t>
+          <t>1680061632.02226</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>1715.021</t>
+          <t>1715021155.42214</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1742.371</t>
+          <t>1742371170.92448</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1655.599</t>
+          <t>1655599317.7131</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>1486.981</t>
+          <t>1486981311.13352</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1534.224</t>
+          <t>1534224253.10563</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1417.246</t>
+          <t>1417246279.20295</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1502.796</t>
+          <t>1502795621.06196</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1553.394</t>
+          <t>1553394037.96908</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1565.821</t>
+          <t>1565820507.37857</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>1559.424</t>
+          <t>1559423979.55232</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>1514.145</t>
+          <t>1514145315.53512</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>1546.655</t>
+          <t>1546655379.8852</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>1412.184</t>
+          <t>1412184378.50881</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>1362.007</t>
+          <t>1362007285.17531</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1118.273</t>
+          <t>1118273407.08978</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1011.926</t>
+          <t>1011925929.17988</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>1046.91</t>
+          <t>1046910164.83589</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>1073.77</t>
+          <t>1073769595.79744</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>1153.152</t>
+          <t>1153151837.15891</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>1065.081</t>
+          <t>1065080566.81118</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>1209.726</t>
+          <t>1209726123.98216</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>1124.83</t>
+          <t>1124830117.29928</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>1301.878</t>
+          <t>1301877728.42393</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>1381.817</t>
+          <t>1381816749.00074</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>1324.942</t>
+          <t>1324941694.3762</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1393.147</t>
+          <t>1393147293.33752</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>83479.278</t>
+          <t>83479278140.4863</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>40657.517</t>
+          <t>40657516500.214</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>44288.748</t>
+          <t>44288747797.553</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>48254.602</t>
+          <t>48254601749.5842</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>47086.258</t>
+          <t>47086258152.7858</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>49645.652</t>
+          <t>49645651870.3693</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>48728.009</t>
+          <t>48728008902.3658</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>47272.992</t>
+          <t>47272992363.1543</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>48295.025</t>
+          <t>48295025223.5038</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>46659.994</t>
+          <t>46659994228.3753</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>47869.131</t>
+          <t>47869130920.3728</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>47888.003</t>
+          <t>47888002648.5093</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>49234.395</t>
+          <t>49234394658.0311</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>49317.058</t>
+          <t>49317058081.8392</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>51541.738</t>
+          <t>51541737591.4704</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>52220.279</t>
+          <t>52220279177.4722</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>53405.106</t>
+          <t>53405105876.4323</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>54074.534</t>
+          <t>54074533985.8808</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>55278.304</t>
+          <t>55278304156.188</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>57485.978</t>
+          <t>57485977844.2091</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>72309.937</t>
+          <t>72309936534.9331</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>63694.636</t>
+          <t>63694636483.596</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>53134.837</t>
+          <t>53134836571.8513</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>66394.381</t>
+          <t>66394380977.118</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>68782.602</t>
+          <t>68782601728.8887</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>73973.31</t>
+          <t>73973310256.7471</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>76168.963</t>
+          <t>76168963440.8086</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>362.668</t>
+          <t>362668025.971221</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>151.119</t>
+          <t>151119221.736034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>170.025</t>
+          <t>170024845.230375</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>174.579</t>
+          <t>174579124.37185</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>178.625</t>
+          <t>178624907.643302</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>181.701</t>
+          <t>181701028.862456</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>189.585</t>
+          <t>189585046.726965</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>153.043</t>
+          <t>153043278.167387</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>185.1</t>
+          <t>185100458.765052</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>170.575</t>
+          <t>170575148.997569</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>174.568</t>
+          <t>174567886.757943</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>172.301</t>
+          <t>172300957.824652</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>168.903</t>
+          <t>168903452.638122</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>169.554</t>
+          <t>169553674.670464</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>167.177</t>
+          <t>167176923.166419</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>163.537</t>
+          <t>163536621.683301</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>168.291</t>
+          <t>168291087.922651</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>170.055</t>
+          <t>170054890.887942</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>169.239</t>
+          <t>169238617.061718</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>195.685</t>
+          <t>195684858.869986</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>216.747</t>
+          <t>216747383.718833</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>221.62</t>
+          <t>221620078.126456</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>244.264</t>
+          <t>244264465.432047</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>275.674</t>
+          <t>275673572.860224</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>325.546</t>
+          <t>325545645.275159</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>330.013</t>
+          <t>330012690.675859</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>343.855</t>
+          <t>343855143.62751</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>8528.73</t>
+          <t>8528730487.76671</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5920.328</t>
+          <t>5920327927.8253</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6330.391</t>
+          <t>6330390757.65572</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>6516.208</t>
+          <t>6516207738.95884</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6741.457</t>
+          <t>6741457376.80964</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>6765.591</t>
+          <t>6765591117.92579</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>6623.707</t>
+          <t>6623707499.09298</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6872.271</t>
+          <t>6872271155.98958</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>6401.231</t>
+          <t>6401230578.22085</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>6841.197</t>
+          <t>6841196850.58517</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>6784.473</t>
+          <t>6784472755.09172</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7099.53</t>
+          <t>7099529555.16053</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>7310.784</t>
+          <t>7310783974.4176</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>7445.418</t>
+          <t>7445418345.50005</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>7221.224</t>
+          <t>7221224236.50341</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>6998.099</t>
+          <t>6998099087.97418</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>6747.478</t>
+          <t>6747477956.75017</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6645.361</t>
+          <t>6645360542.82386</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>6676.53</t>
+          <t>6676529638.78733</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>6329.503</t>
+          <t>6329503465.21963</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>6390.788</t>
+          <t>6390788293.13033</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>6391.904</t>
+          <t>6391904283.1422</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>6280.905</t>
+          <t>6280904838.81881</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6368.45</t>
+          <t>6368450377.92959</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>6554.063</t>
+          <t>6554062891.71286</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>6731.11</t>
+          <t>6731109802.25339</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>6821.745</t>
+          <t>6821745149.56762</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>27401.062</t>
+          <t>27401062394.848</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>24682.576</t>
+          <t>24682576053.2607</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>24654.469</t>
+          <t>24654468550.9541</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>24179.743</t>
+          <t>24179743084.6151</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23709.961</t>
+          <t>23709961151.6464</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>22773.456</t>
+          <t>22773455835.4918</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>22762.257</t>
+          <t>22762257180.3834</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>21823.198</t>
+          <t>21823198278.0218</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20891.09</t>
+          <t>20891089878.8488</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20256.424</t>
+          <t>20256423932.9105</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>20311.478</t>
+          <t>20311477648.8416</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>20643.516</t>
+          <t>20643515855.021</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>21226.859</t>
+          <t>21226858976.1611</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>21850.753</t>
+          <t>21850753083.4891</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>21975.901</t>
+          <t>21975901319.7182</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>21463.14</t>
+          <t>21463140083.7851</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>20755.76</t>
+          <t>20755760296.6617</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>20663.98</t>
+          <t>20663979934.6847</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>20662.181</t>
+          <t>20662180852.0003</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>20404.521</t>
+          <t>20404521274.2588</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>20599.359</t>
+          <t>20599359487.0909</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>20757.34</t>
+          <t>20757340297.8377</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>20242.016</t>
+          <t>20242015806.0569</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>22858.802</t>
+          <t>22858801766.4822</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>22986.423</t>
+          <t>22986423068.7217</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>24724.23</t>
+          <t>24724229781.0024</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>25754.028</t>
+          <t>25754028144.4876</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5614.037</t>
+          <t>5614036586.4669</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>5791.689</t>
+          <t>5791688803.5313</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>5618.806</t>
+          <t>5618805797.10527</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>5649.137</t>
+          <t>5649136522.37644</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6290.426</t>
+          <t>6290426218.76172</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>6227.083</t>
+          <t>6227083275.7721</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6223.76</t>
+          <t>6223760206.72148</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>6353.297</t>
+          <t>6353296543.22858</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>6309.075</t>
+          <t>6309074988.17043</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>6161.382</t>
+          <t>6161382055.22518</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>6187.305</t>
+          <t>6187304686.74404</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>6068.134</t>
+          <t>6068134008.66522</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>6111.691</t>
+          <t>6111690677.31266</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>6027.18</t>
+          <t>6027179916.22491</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>5806.146</t>
+          <t>5806146424.61431</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>5656.977</t>
+          <t>5656976788.88921</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>5564.509</t>
+          <t>5564508731.23222</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>5342.514</t>
+          <t>5342513551.08315</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>5083.995</t>
+          <t>5083994891.65147</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>5078.02</t>
+          <t>5078020039.53497</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>5004.71</t>
+          <t>5004709656.23218</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>5124.843</t>
+          <t>5124842535.79732</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>5185.768</t>
+          <t>5185768191.04565</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5503.53</t>
+          <t>5503529757.66318</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>5579.618</t>
+          <t>5579618199.85154</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>5748.151</t>
+          <t>5748150887.02953</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>5763.993</t>
+          <t>5763992645.55895</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>19355.575</t>
+          <t>19355574755.6787</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>16401.46</t>
+          <t>16401459999.9939</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16116.124</t>
+          <t>16116123999.9944</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>18931.889</t>
+          <t>18931889000.0052</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>18893.271</t>
+          <t>18893270999.993</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>18779.61</t>
+          <t>18779609999.9995</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>18794.607</t>
+          <t>18794606999.9988</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>17558.633</t>
+          <t>17558633000.0021</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>15875.885</t>
+          <t>15875884999.9998</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>15136.32</t>
+          <t>15136320000.0037</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>15144.354</t>
+          <t>15144353999.9995</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>13876.449</t>
+          <t>13876448999.998</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>14441.88</t>
+          <t>14441880000.0003</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>14397.269</t>
+          <t>14397268999.9982</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>13965.587</t>
+          <t>13965587000.0045</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>13533.889</t>
+          <t>13533888999.9992</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>13393.992</t>
+          <t>13393991999.9994</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>12976.36</t>
+          <t>12976359999.9989</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>12330.483</t>
+          <t>12330482999.9994</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>14444.81</t>
+          <t>14444809864.8466</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>14011.733</t>
+          <t>14011732622.9355</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>14885.507</t>
+          <t>14885507435.9922</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>14981.409</t>
+          <t>14981409205.639</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16303.296</t>
+          <t>16303295765.8486</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>17673.592</t>
+          <t>17673591675.0768</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>19747.883</t>
+          <t>19747882977.2855</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>19152.75</t>
+          <t>19152750044.9779</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>80739.509</t>
+          <t>80739509062.7692</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>83986.867</t>
+          <t>83986866511.4751</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>80268.759</t>
+          <t>80268759023.1491</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>74753.416</t>
+          <t>74753416298.3044</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>75511.704</t>
+          <t>75511703683.5337</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>85794.032</t>
+          <t>85794031660.1638</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>87482.098</t>
+          <t>87482098056.9528</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>79147.286</t>
+          <t>79147286229.6637</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>84187.422</t>
+          <t>84187422437.2154</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>86480.907</t>
+          <t>86480907152.3252</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>78477.531</t>
+          <t>78477531222.3691</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>86762.236</t>
+          <t>86762236126.4411</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>85183.004</t>
+          <t>85183004276.0493</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>87090.635</t>
+          <t>87090635244.331</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>83382.607</t>
+          <t>83382607433.3707</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>82886.876</t>
+          <t>82886875653.3383</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>85423.485</t>
+          <t>85423485410.7543</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>73962.264</t>
+          <t>73962263951.8224</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>86871.547</t>
+          <t>86871546866.4309</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>87850.619</t>
+          <t>87850619276.64</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>74750.734</t>
+          <t>74750734185.4211</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>61066.05</t>
+          <t>61066050099.2417</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>59142.415</t>
+          <t>59142414690.4101</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>68459.196</t>
+          <t>68459195978.2495</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>71172.053</t>
+          <t>71172053391.8285</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>73309.649</t>
+          <t>73309649309.9521</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>74683.928</t>
+          <t>74683927616.3342</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>4180.033</t>
+          <t>4180033178.88235</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3461.773</t>
+          <t>3461773045.38608</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3573.029</t>
+          <t>3573029439.50796</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>3553.288</t>
+          <t>3553288227.20968</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>3481.129</t>
+          <t>3481128797.97789</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>3315.785</t>
+          <t>3315784822.22999</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>3167.023</t>
+          <t>3167022543.89208</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>3140.558</t>
+          <t>3140557921.75691</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>3120.919</t>
+          <t>3120919174.84661</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>3131.497</t>
+          <t>3131497086.04714</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>3114.125</t>
+          <t>3114125268.08388</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3198.197</t>
+          <t>3198197272.74274</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>3226.201</t>
+          <t>3226201454.19852</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>3321.523</t>
+          <t>3321523385.99257</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>3265.83</t>
+          <t>3265830380.49817</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>3007.054</t>
+          <t>3007053684.81211</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>2953.14</t>
+          <t>2953140292.11557</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2976.098</t>
+          <t>2976098260.3016</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2995.81</t>
+          <t>2995810145.95636</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>2969.839</t>
+          <t>2969838679.18455</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>3088.613</t>
+          <t>3088613390.88668</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>3242.437</t>
+          <t>3242436922.46152</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>3153.935</t>
+          <t>3153934685.0646</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3420.482</t>
+          <t>3420481980.29706</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>3473.711</t>
+          <t>3473710639.63694</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>3589.832</t>
+          <t>3589832259.88925</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>3768.191</t>
+          <t>3768190725.44494</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1350.062</t>
+          <t>1350062086.94366</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1439.618</t>
+          <t>1439617552.23849</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1411.799</t>
+          <t>1411799422.43922</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1373.275</t>
+          <t>1373274744.34657</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>1358.725</t>
+          <t>1358724544.9178</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>1327.363</t>
+          <t>1327362765.59105</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1294.99</t>
+          <t>1294989539.98814</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>1324.508</t>
+          <t>1324507573.57043</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1341.431</t>
+          <t>1341430935.89152</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>1257.684</t>
+          <t>1257683639.47811</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>1306.669</t>
+          <t>1306668534.05806</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>1348.085</t>
+          <t>1348085071.69752</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>1335.895</t>
+          <t>1335894856.05969</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>1377.885</t>
+          <t>1377885375.39101</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>1330.287</t>
+          <t>1330286517.56478</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1250.686</t>
+          <t>1250686343.82542</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1216.328</t>
+          <t>1216327979.88867</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>1164.937</t>
+          <t>1164936847.9357</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>1140.684</t>
+          <t>1140684173.49504</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>1135.158</t>
+          <t>1135158261.54193</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>1101.667</t>
+          <t>1101666531.96655</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>1102.228</t>
+          <t>1102228174.58453</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>1125.446</t>
+          <t>1125445808.10566</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1155.474</t>
+          <t>1155474315.76638</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>1260.274</t>
+          <t>1260273893.87133</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>1273.333</t>
+          <t>1273332607.38663</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>1346.784</t>
+          <t>1346784034.50052</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>4350.276</t>
+          <t>4350276248.42139</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4567.882</t>
+          <t>4567881756.77234</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4579.921</t>
+          <t>4579920619.57635</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>4658.563</t>
+          <t>4658562574.22012</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4273.272</t>
+          <t>4273272034.04765</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4809.218</t>
+          <t>4809218385.27428</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>4837.664</t>
+          <t>4837663679.3448</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4708.475</t>
+          <t>4708475464.77087</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4752.77</t>
+          <t>4752769955.4423</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4660.697</t>
+          <t>4660696757.37294</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>4662.309</t>
+          <t>4662308544.91117</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>4790.043</t>
+          <t>4790042669.01857</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>4852.018</t>
+          <t>4852017747.11251</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>4924.432</t>
+          <t>4924432320.37268</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>4843.281</t>
+          <t>4843281370.33485</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>4634.178</t>
+          <t>4634178313.16057</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>4748.118</t>
+          <t>4748117928.09568</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>4806.091</t>
+          <t>4806091093.38963</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>4794.609</t>
+          <t>4794608554.45546</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>4742.428</t>
+          <t>4742428009.12554</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>4549.064</t>
+          <t>4549064397.28838</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>4598.724</t>
+          <t>4598724052.19878</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>4433.977</t>
+          <t>4433976575.64493</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>4508.912</t>
+          <t>4508912466.54464</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>4451.371</t>
+          <t>4451371144.68868</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>4481.164</t>
+          <t>4481163728.41522</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>4341.646</t>
+          <t>4341645938.59492</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>35767.368</t>
+          <t>35767368030.5977</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>33376.79</t>
+          <t>33376789602.9773</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>34299.11</t>
+          <t>34299110001.4249</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>34150.87</t>
+          <t>34150869975.5982</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>34873.608</t>
+          <t>34873608131.8356</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>35300.773</t>
+          <t>35300773486.3917</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34280.229</t>
+          <t>34280228628.9184</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>36697.38</t>
+          <t>36697379775.9861</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>35233.437</t>
+          <t>35233437387.6697</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>34359.983</t>
+          <t>34359982826.1968</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>35734.852</t>
+          <t>35734852141.4363</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>36723.451</t>
+          <t>36723450812.9005</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>32759.414</t>
+          <t>32759413628.781</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>31476.829</t>
+          <t>31476829128.2277</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>32416.123</t>
+          <t>32416123471.8209</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>30692.878</t>
+          <t>30692878464.4028</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>32739.665</t>
+          <t>32739665103.5797</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>35155.732</t>
+          <t>35155732234.5845</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>36890.024</t>
+          <t>36890023650.1036</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>35218.032</t>
+          <t>35218031904.9846</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>32777.778</t>
+          <t>32777777652.5409</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>37399.916</t>
+          <t>37399915787.6327</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>35742.283</t>
+          <t>35742282555.5029</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>34259.111</t>
+          <t>34259110876.4365</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>29476.624</t>
+          <t>29476624169.2194</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>30766.391</t>
+          <t>30766391346.6933</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>30801.34</t>
+          <t>30801339783.5226</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>16826.727</t>
+          <t>16826727086.9132</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>13440.532</t>
+          <t>13440531911.8876</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>13497.393</t>
+          <t>13497393414.3846</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>13506.764</t>
+          <t>13506764147.3701</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>12867.277</t>
+          <t>12867277325.8582</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>12663.614</t>
+          <t>12663613811.4688</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>12638.941</t>
+          <t>12638941336.2515</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>10526.542</t>
+          <t>10526541694.9589</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>11543.643</t>
+          <t>11543643190.7242</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>12185.624</t>
+          <t>12185624340.9121</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>12468.315</t>
+          <t>12468314786.4952</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>11965.559</t>
+          <t>11965559389.2409</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>12777.922</t>
+          <t>12777921603.6575</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>12541.367</t>
+          <t>12541367470.2039</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>11821.104</t>
+          <t>11821103809.486</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>12286.976</t>
+          <t>12286975811.6268</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>11735.223</t>
+          <t>11735223045.6256</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>13330.713</t>
+          <t>13330713371.7834</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>13399.744</t>
+          <t>13399743981.3375</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>12789.492</t>
+          <t>12789492480.2946</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>13063.711</t>
+          <t>13063711222.2542</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>14930.775</t>
+          <t>14930775431.1644</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>14892.258</t>
+          <t>14892257696.9264</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15678.475</t>
+          <t>15678474782.8162</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>15235.198</t>
+          <t>15235198152.7272</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16217.696</t>
+          <t>16217696303.3315</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>15896.039</t>
+          <t>15896038586.6582</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>148203.362</t>
+          <t>148203361664.195</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>102483.591</t>
+          <t>102483590853.026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>103451.425</t>
+          <t>103451424727.265</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>83729.389</t>
+          <t>83729388755.3488</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>106722.628</t>
+          <t>106722628170.429</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>107378.973</t>
+          <t>107378972961.741</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>107843.362</t>
+          <t>107843361958.458</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>107148.133</t>
+          <t>107148132781.07</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>106190.847</t>
+          <t>106190846543.235</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>80376.956</t>
+          <t>80376956108.1685</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>106795.963</t>
+          <t>106795963481.431</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>81380.033</t>
+          <t>81380033016.3481</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>110210.462</t>
+          <t>110210461789.823</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>111125.848</t>
+          <t>111125847764.404</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>109712.203</t>
+          <t>109712202967.763</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>102758.279</t>
+          <t>102758279168.117</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>102519.202</t>
+          <t>102519202313.126</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>73124.252</t>
+          <t>73124251611.7343</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>105595.2</t>
+          <t>105595200043.543</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>98057.095</t>
+          <t>98057095287.9337</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>101115.907</t>
+          <t>101115906743.951</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>128259.289</t>
+          <t>128259289478.136</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>129572.633</t>
+          <t>129572633148.829</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>134298.373</t>
+          <t>134298372909.318</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>135388.189</t>
+          <t>135388189074.549</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>142143.785</t>
+          <t>142143785459.24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>144532.23</t>
+          <t>144532230392.592</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8050307.111</t>
+          <t>8050307111481.52</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4047495.086</t>
+          <t>4047495086127.72</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4109001.932</t>
+          <t>4109001931640.88</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>4150720.755</t>
+          <t>4150720755378.24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4201220.71</t>
+          <t>4201220709579.23</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4264966.243</t>
+          <t>4264966243075.6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>4299019.827</t>
+          <t>4299019827271.16</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4349119.533</t>
+          <t>4349119532746.19</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4395374.009</t>
+          <t>4395374009420.79</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4429418.709</t>
+          <t>4429418709391.17</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>4497459.042</t>
+          <t>4497459042005.93</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4552546.417</t>
+          <t>4552546416667.94</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>4621118.608</t>
+          <t>4621118608214.69</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>4670881.471</t>
+          <t>4670881471206.42</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>4624773.044</t>
+          <t>4624773044027.57</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>4650440.744</t>
+          <t>4650440744015.68</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>4735438.675</t>
+          <t>4735438674901.98</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>4746116.736</t>
+          <t>4746116735810.5</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>4850256.253</t>
+          <t>4850256252732.54</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>4886221.843</t>
+          <t>4886221843155.83</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>4935592.646</t>
+          <t>4935592646444.66</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>5555449.259</t>
+          <t>5555449259346.76</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>5546189.228</t>
+          <t>5546189228144.11</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>5862121.252</t>
+          <t>5862121252276.54</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>5925058.06</t>
+          <t>5925058059746.98</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>6440999.348</t>
+          <t>6440999347850.1</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>6704218.937</t>
+          <t>6704218936548.77</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1849.226</t>
+          <t>1849226044.14005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2150.502</t>
+          <t>2150502000.00019</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2142.933</t>
+          <t>2142933100.81933</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2267.423</t>
+          <t>2267423086.70145</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2204.007</t>
+          <t>2204006906.03294</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2061.075</t>
+          <t>2061075033.37015</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2146.57</t>
+          <t>2146570224.00174</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2068.624</t>
+          <t>2068623987.24492</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2131.149</t>
+          <t>2131149009.17069</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2154.507</t>
+          <t>2154507150.27565</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2233.093</t>
+          <t>2233093085.9184</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2169.333</t>
+          <t>2169332914.8373</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>2094.746</t>
+          <t>2094745621.10503</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2176.996</t>
+          <t>2176995954.69611</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2080.641</t>
+          <t>2080641398.41753</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>2014.698</t>
+          <t>2014697990.01005</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1922.372</t>
+          <t>1922371744.23585</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>1864.368</t>
+          <t>1864367745.3267</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>1788.916</t>
+          <t>1788915748.59445</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>1689.141</t>
+          <t>1689140520.3615</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>1667.396</t>
+          <t>1667395884.26429</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>1652.259</t>
+          <t>1652258696.66309</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>1725.345</t>
+          <t>1725345356.25661</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1763.988</t>
+          <t>1763987567.45977</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>1808.412</t>
+          <t>1808411635.24193</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>1812.023</t>
+          <t>1812022750.18887</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>1879.692</t>
+          <t>1879691519.98774</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3969.417</t>
+          <t>3969417033.96925</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>3873.845</t>
+          <t>3873844810.18103</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>3222.575</t>
+          <t>3222575026.43786</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>3830.498</t>
+          <t>3830497502.61591</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>3813.4</t>
+          <t>3813399852.46872</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3231.886</t>
+          <t>3231886289.89403</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>3299.407</t>
+          <t>3299407378.05097</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>3445.947</t>
+          <t>3445947246.06913</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>3286.954</t>
+          <t>3286953735.62447</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>4053.552</t>
+          <t>4053551507.67566</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>3249.612</t>
+          <t>3249611901.7969</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3312.649</t>
+          <t>3312648947.16651</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>3379.39</t>
+          <t>3379389963.47423</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>4278.936</t>
+          <t>4278935923.76262</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>3268.448</t>
+          <t>3268448244.76859</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>4158.229</t>
+          <t>4158229449.9808</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>3261.063</t>
+          <t>3261062547.89657</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>4224.765</t>
+          <t>4224765023.85764</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>4229.12</t>
+          <t>4229120337.40019</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>3976.799</t>
+          <t>3976798802.46333</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>3922.247</t>
+          <t>3922246556.20656</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>4129.978</t>
+          <t>4129977949.01936</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>4149.127</t>
+          <t>4149127325.37505</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3944.067</t>
+          <t>3944066649.16846</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>3753.519</t>
+          <t>3753519366.90519</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>3874.107</t>
+          <t>3874106696.08614</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>3986.103</t>
+          <t>3986103200.33349</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2306.608</t>
+          <t>2306608239.12881</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2379.03</t>
+          <t>2379030316.61819</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2439.745</t>
+          <t>2439744783.86461</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2547.391</t>
+          <t>2547390701.76924</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2562.185</t>
+          <t>2562185381.78959</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2572.705</t>
+          <t>2572704862.4676</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2467.307</t>
+          <t>2467307486.01689</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2495.375</t>
+          <t>2495375236.36515</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2597.032</t>
+          <t>2597031927.67426</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2402.748</t>
+          <t>2402747818.03062</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2404.506</t>
+          <t>2404506101.94687</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2504.527</t>
+          <t>2504527135.90774</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>2579.328</t>
+          <t>2579327757.13844</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2668.709</t>
+          <t>2668709306.03337</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2613.462</t>
+          <t>2613462474.38029</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>2650.862</t>
+          <t>2650862030.99653</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>2654.138</t>
+          <t>2654137663.86993</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>2754.303</t>
+          <t>2754302570.38085</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>2758.808</t>
+          <t>2758807909.59223</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>2727.078</t>
+          <t>2727078135.45621</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>2595.306</t>
+          <t>2595306066.55591</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>2381.989</t>
+          <t>2381989447.92964</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2260.555</t>
+          <t>2260555320.35504</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2271.705</t>
+          <t>2271704797.23382</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2229.337</t>
+          <t>2229336703.22953</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2202.624</t>
+          <t>2202623747.45922</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>2299.393</t>
+          <t>2299393395.4761</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>15768.052</t>
+          <t>15768052202.4669</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>17446.898</t>
+          <t>17446898183.614</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>17372.303</t>
+          <t>17372303175.3916</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17037.752</t>
+          <t>17037751610.278</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>16095.312</t>
+          <t>16095312479.528</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>15408.238</t>
+          <t>15408238359.5727</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>13493.923</t>
+          <t>13493922926.6283</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>12828.569</t>
+          <t>12828569208.0599</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>13375.088</t>
+          <t>13375087784.4623</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>13058.212</t>
+          <t>13058212307.5912</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>13139.587</t>
+          <t>13139586575.5124</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>13050.933</t>
+          <t>13050933081.9567</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>13860.963</t>
+          <t>13860962948.7082</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>14543.848</t>
+          <t>14543848216.4127</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>14244.532</t>
+          <t>14244531668.4403</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>13612.341</t>
+          <t>13612341250.9754</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>13524.927</t>
+          <t>13524926834.5554</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>14261.76</t>
+          <t>14261759865.9517</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>14508.978</t>
+          <t>14508977932.0209</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>12707.488</t>
+          <t>12707487501.0064</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>12227.258</t>
+          <t>12227257628.4404</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>13205.257</t>
+          <t>13205257230.9009</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>13068.755</t>
+          <t>13068755480.3407</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13322.566</t>
+          <t>13322565859.8688</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>13842.083</t>
+          <t>13842083388.1512</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14022.366</t>
+          <t>14022365748.7864</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>13800.195</t>
+          <t>13800195404.356</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1220990.729</t>
+          <t>1220990729132.52</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>454488.727</t>
+          <t>454488727323.507</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>480458.906</t>
+          <t>480458906485.63</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>507491.95</t>
+          <t>507491949557.512</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>575015.406</t>
+          <t>575015405518.453</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>584461.443</t>
+          <t>584461442908.181</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>589009.69</t>
+          <t>589009689984.474</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>625867.633</t>
+          <t>625867633041.36</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>660011.695</t>
+          <t>660011695440.561</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>707866.177</t>
+          <t>707866176987.172</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>740474.911</t>
+          <t>740474911175.022</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>735700.727</t>
+          <t>735700726743.084</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>746339.786</t>
+          <t>746339786150.129</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>808703.197</t>
+          <t>808703197417.7</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>809454.226</t>
+          <t>809454225960.818</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>847151.569</t>
+          <t>847151569360.673</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>853075.169</t>
+          <t>853075168633.191</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>857129.049</t>
+          <t>857129049269.262</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>868858.094</t>
+          <t>868858094301.398</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>859194.597</t>
+          <t>859194596719.236</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>836631.938</t>
+          <t>836631937754.266</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>899116.466</t>
+          <t>899116465951.566</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>891422.463</t>
+          <t>891422462840.827</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>910561.039</t>
+          <t>910561039331.3</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>900447.78</t>
+          <t>900447780163.038</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>966997.736</t>
+          <t>966997735588.094</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1004775.005</t>
+          <t>1004775005076.64</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>173122.68</t>
+          <t>173122680447.92</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>137026.637</t>
+          <t>137026637256.195</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>139159.687</t>
+          <t>139159687445.371</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>143519.375</t>
+          <t>143519375020.976</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>140906.192</t>
+          <t>140906192011.979</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>140301.88</t>
+          <t>140301880438.488</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>143613.617</t>
+          <t>143613616888.841</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>144390.499</t>
+          <t>144390499191.984</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>151677.9</t>
+          <t>151677900265.414</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>153928.915</t>
+          <t>153928914847.872</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>152043.45</t>
+          <t>152043449598.243</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>155719.758</t>
+          <t>155719758426.231</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>159369.814</t>
+          <t>159369813726.084</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>171296.713</t>
+          <t>171296712919.681</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>179456.734</t>
+          <t>179456733537.71</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>186906.739</t>
+          <t>186906738733.41</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>197793.275</t>
+          <t>197793274933.781</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>194215.41</t>
+          <t>194215410048.117</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>196440.901</t>
+          <t>196440901116.707</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>185010.753</t>
+          <t>185010753299.696</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>177828.79</t>
+          <t>177828790167.523</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>200305.94</t>
+          <t>200305940004.544</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>183570.124</t>
+          <t>183570124436.149</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>186460.198</t>
+          <t>186460197937.079</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>166487.218</t>
+          <t>166487218419.219</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>163318.285</t>
+          <t>163318284854.807</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>158065.76</t>
+          <t>158065759734.688</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>309410.529</t>
+          <t>309410529092.62</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>229547.78</t>
+          <t>229547780456.806</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>228763.777</t>
+          <t>228763776664.902</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>235866.516</t>
+          <t>235866516312.603</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>234143.928</t>
+          <t>234143927940.815</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>228257.462</t>
+          <t>228257461604.855</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>210013.06</t>
+          <t>210013060346.425</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>224935.969</t>
+          <t>224935969271.409</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>239743.099</t>
+          <t>239743099246.25</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>230413.134</t>
+          <t>230413133807.557</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>228471.681</t>
+          <t>228471681396.683</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>239411.477</t>
+          <t>239411477483.952</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>243379.966</t>
+          <t>243379965572.21</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>230507.349</t>
+          <t>230507348573.481</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>229442.787</t>
+          <t>229442787217.714</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>254366.003</t>
+          <t>254366002761.705</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>231655.457</t>
+          <t>231655457150.798</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>231507.695</t>
+          <t>231507695227.327</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>233217.21</t>
+          <t>233217210233.307</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>238145.695</t>
+          <t>238145695457.392</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>205706.431</t>
+          <t>205706430891.696</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>192505.881</t>
+          <t>192505880532.335</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>190764.789</t>
+          <t>190764788746.327</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>213194.949</t>
+          <t>213194948622.828</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>226873.056</t>
+          <t>226873055852.169</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>252800.713</t>
+          <t>252800712709.948</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>259871.643</t>
+          <t>259871642696.423</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>947884.352</t>
+          <t>947884351967.033</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>437306.287</t>
+          <t>437306286728.229</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>446751.528</t>
+          <t>446751527685.21</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>464330.265</t>
+          <t>464330265173.903</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>470510.592</t>
+          <t>470510591897.853</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>490990.109</t>
+          <t>490990108633.345</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>490284.296</t>
+          <t>490284296438.545</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>505913.221</t>
+          <t>505913221293.333</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>524016.074</t>
+          <t>524016073544.629</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>533214.889</t>
+          <t>533214889213.811</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>548623.227</t>
+          <t>548623227006.306</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>562151.381</t>
+          <t>562151381457.801</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>572457.238</t>
+          <t>572457237873.269</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>600480.205</t>
+          <t>600480205026.043</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>612190.087</t>
+          <t>612190087117.027</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>625743.35</t>
+          <t>625743350147.808</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>651903.074</t>
+          <t>651903073952.974</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>661997.376</t>
+          <t>661997375901.575</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>680543.536</t>
+          <t>680543535909.779</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>714831.401</t>
+          <t>714831401029</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>725600.441</t>
+          <t>725600440858.234</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>789857.089</t>
+          <t>789857089338.742</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>751294.696</t>
+          <t>751294696040.454</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>767262.498</t>
+          <t>767262497513.319</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>770176.772</t>
+          <t>770176771811.698</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>845519.501</t>
+          <t>845519500719.879</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>865021.753</t>
+          <t>865021753330.221</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>72492.798</t>
+          <t>72492797702.0372</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>30750.464</t>
+          <t>30750463715.6797</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>30958.981</t>
+          <t>30958981400.4419</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>31339.598</t>
+          <t>31339597802.2018</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>30274.658</t>
+          <t>30274657789.4146</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>31682.124</t>
+          <t>31682123766.1293</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>30866.674</t>
+          <t>30866673740.268</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>37239.448</t>
+          <t>37239448392.1099</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>37526.16</t>
+          <t>37526160070.6914</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>41553.192</t>
+          <t>41553192289.9087</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>44402.189</t>
+          <t>44402189097.179</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>47950.534</t>
+          <t>47950534304.4174</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>55931.182</t>
+          <t>55931181565.9988</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>59465.535</t>
+          <t>59465535152.1654</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>59325.882</t>
+          <t>59325881995.4232</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>62826.284</t>
+          <t>62826284098.3674</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>62725.398</t>
+          <t>62725398158.2494</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>62820.324</t>
+          <t>62820324439.7946</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>64890.309</t>
+          <t>64890308507.2168</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>60763.928</t>
+          <t>60763928171.8191</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>57321.816</t>
+          <t>57321816152.9635</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>58342.618</t>
+          <t>58342617924.959</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>57165.263</t>
+          <t>57165263402.1823</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>58188.081</t>
+          <t>58188080932.1679</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>60216.742</t>
+          <t>60216742148.0575</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>65805.008</t>
+          <t>65805007788.5883</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>68412.58</t>
+          <t>68412580028.8597</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>gdp.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
